--- a/docs/Sets_Arc1_Arc2.xlsx
+++ b/docs/Sets_Arc1_Arc2.xlsx
@@ -1,13 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{208B688D-5840-4713-A528-6D9669281EFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView minimized="1" xWindow="4290" yWindow="4290" windowWidth="28800" windowHeight="15345" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Arc 1 (existant)" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Arc 2 (à définir)" state="visible" r:id="rId5"/>
+    <sheet name="Arc 1 (existant)" sheetId="1" r:id="rId1"/>
+    <sheet name="Arc 2 (à définir)" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -326,9 +343,6 @@
     <t>P1</t>
   </si>
   <si>
-    <t>+X % de dégâts PHYSIQUES</t>
-  </si>
-  <si>
     <t>damageType = physical / value = ?</t>
   </si>
   <si>
@@ -347,12 +361,6 @@
     <t>Socle — dégâts magiques</t>
   </si>
   <si>
-    <t>+X % de dégâts ARCANIQUES</t>
-  </si>
-  <si>
-    <t>damageType = arcane / value = ?</t>
-  </si>
-  <si>
     <t>QUESTION OUVERTE : garde-t-on aussi feu et poison comme axes séparés ?</t>
   </si>
   <si>
@@ -365,9 +373,6 @@
     <t>Socle — soins</t>
   </si>
   <si>
-    <t>+X % de soins prodigués</t>
-  </si>
-  <si>
     <t>heal_amp</t>
   </si>
   <si>
@@ -768,59 +773,71 @@
   </si>
   <si>
     <t>TOTAL sets Arc 2</t>
+  </si>
+  <si>
+    <t>X % de dégâts MAGIQUE</t>
+  </si>
+  <si>
+    <t>X % de dégâts PHYSIQUES</t>
+  </si>
+  <si>
+    <t>damageType = magique / value = ?</t>
+  </si>
+  <si>
+    <t>X % de soins prodigués</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="13" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="14"/>
       <color rgb="FF1F3864"/>
-      <sz val="14"/>
       <name val="Arial"/>
     </font>
     <font>
       <i/>
+      <sz val="9"/>
       <color rgb="FF595959"/>
-      <sz val="9"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
       <i/>
+      <sz val="10"/>
       <color rgb="FF595959"/>
-      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color rgb="FFC00000"/>
-      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="9"/>
       <color rgb="FFC00000"/>
-      <sz val="9"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color rgb="FF1F3864"/>
-      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -829,14 +846,14 @@
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color rgb="FF375623"/>
-      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FF1F3864"/>
-      <sz val="11"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -907,9 +924,6 @@
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -934,6 +948,9 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1272,9 +1289,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q21"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -1291,585 +1308,585 @@
     <col min="17" max="17" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:17" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="4" ht="30" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+    </row>
+    <row r="4" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="L4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="M4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="N4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="O4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="P4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="Q4" s="3" t="s">
+      <c r="Q4" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="3">
         <v>4</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I5" s="3">
         <v>0</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="3">
         <v>0</v>
       </c>
-      <c r="K5" s="4">
+      <c r="K5" s="3">
         <v>250</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="L5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="M5" s="4" t="s">
+      <c r="M5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N5" s="4" t="s">
+      <c r="N5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="O5" s="4" t="s">
+      <c r="O5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="P5" s="4" t="s">
+      <c r="P5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="Q5" s="4" t="s">
+      <c r="Q5" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="3">
         <v>4</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="4">
+      <c r="I6" s="3">
         <v>40</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="3">
         <v>0</v>
       </c>
-      <c r="K6" s="4">
+      <c r="K6" s="3">
         <v>0</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="L6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="M6" s="4" t="s">
+      <c r="M6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="N6" s="4" t="s">
+      <c r="N6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="O6" s="4" t="s">
+      <c r="O6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="P6" s="4" t="s">
+      <c r="P6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="Q6" s="4" t="s">
+      <c r="Q6" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="3">
         <v>4</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="I7" s="4">
+      <c r="I7" s="3">
         <v>30</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7" s="3">
         <v>0</v>
       </c>
-      <c r="K7" s="4">
+      <c r="K7" s="3">
         <v>0</v>
       </c>
-      <c r="L7" s="4" t="s">
+      <c r="L7" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="M7" s="4" t="s">
+      <c r="M7" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="N7" s="4" t="s">
+      <c r="N7" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="O7" s="4" t="s">
+      <c r="O7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="P7" s="4" t="s">
+      <c r="P7" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="Q7" s="4" t="s">
+      <c r="Q7" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="3">
         <v>2</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="I8" s="4">
+      <c r="I8" s="3">
         <v>0</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J8" s="3">
         <v>30</v>
       </c>
-      <c r="K8" s="4">
+      <c r="K8" s="3">
         <v>150</v>
       </c>
-      <c r="L8" s="4" t="s">
+      <c r="L8" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="M8" s="4" t="s">
+      <c r="M8" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="N8" s="4" t="s">
+      <c r="N8" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="O8" s="4" t="s">
+      <c r="O8" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="P8" s="4" t="s">
+      <c r="P8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="Q8" s="4" t="s">
+      <c r="Q8" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+    <row r="9" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="3">
         <v>2</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="I9" s="4">
+      <c r="I9" s="3">
         <v>25</v>
       </c>
-      <c r="J9" s="4">
+      <c r="J9" s="3">
         <v>0</v>
       </c>
-      <c r="K9" s="4">
+      <c r="K9" s="3">
         <v>100</v>
       </c>
-      <c r="L9" s="4" t="s">
+      <c r="L9" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="M9" s="4" t="s">
+      <c r="M9" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="N9" s="4" t="s">
+      <c r="N9" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="O9" s="4" t="s">
+      <c r="O9" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="P9" s="4" t="s">
+      <c r="P9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="Q9" s="4" t="s">
+      <c r="Q9" s="3" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+    <row r="10" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="3">
         <v>2</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="I10" s="4">
+      <c r="I10" s="3">
         <v>30</v>
       </c>
-      <c r="J10" s="4">
+      <c r="J10" s="3">
         <v>0</v>
       </c>
-      <c r="K10" s="4">
+      <c r="K10" s="3">
         <v>0</v>
       </c>
-      <c r="L10" s="4" t="s">
+      <c r="L10" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="M10" s="4" t="s">
+      <c r="M10" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="N10" s="4" t="s">
+      <c r="N10" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="O10" s="4" t="s">
+      <c r="O10" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="P10" s="4" t="s">
+      <c r="P10" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="Q10" s="4" t="s">
+      <c r="Q10" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+    <row r="11" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="3">
         <v>2</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="I11" s="4">
+      <c r="I11" s="3">
         <v>30</v>
       </c>
-      <c r="J11" s="4">
+      <c r="J11" s="3">
         <v>0</v>
       </c>
-      <c r="K11" s="4">
+      <c r="K11" s="3">
         <v>0</v>
       </c>
-      <c r="L11" s="4" t="s">
+      <c r="L11" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="M11" s="4" t="s">
+      <c r="M11" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="N11" s="4" t="s">
+      <c r="N11" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="O11" s="4" t="s">
+      <c r="O11" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="P11" s="4" t="s">
+      <c r="P11" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="Q11" s="4" t="s">
+      <c r="Q11" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+    <row r="12" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="3">
         <v>2</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="I12" s="4">
+      <c r="I12" s="3">
         <v>30</v>
       </c>
-      <c r="J12" s="4">
+      <c r="J12" s="3">
         <v>0</v>
       </c>
-      <c r="K12" s="4">
+      <c r="K12" s="3">
         <v>0</v>
       </c>
-      <c r="L12" s="4" t="s">
+      <c r="L12" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="M12" s="4" t="s">
+      <c r="M12" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="N12" s="4" t="s">
+      <c r="N12" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="O12" s="4" t="s">
+      <c r="O12" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="P12" s="4" t="s">
+      <c r="P12" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="Q12" s="4" t="s">
+      <c r="Q12" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+    <row r="13" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="3">
         <v>2</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="H13" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="I13" s="4">
+      <c r="I13" s="3">
         <v>30</v>
       </c>
-      <c r="J13" s="4">
+      <c r="J13" s="3">
         <v>0</v>
       </c>
-      <c r="K13" s="4">
+      <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="4" t="s">
+      <c r="L13" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="M13" s="4" t="s">
+      <c r="M13" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="N13" s="4" t="s">
+      <c r="N13" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="O13" s="4" t="s">
+      <c r="O13" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="P13" s="4" t="s">
+      <c r="P13" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="Q13" s="4" t="s">
+      <c r="Q13" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="5" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="5" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="5" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="5" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="5" t="s">
         <v>96</v>
       </c>
     </row>
@@ -1878,14 +1895,14 @@
     <mergeCell ref="A2:H2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q47"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -1902,1214 +1919,1214 @@
     <col min="17" max="17" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:17" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="4" ht="30" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+    </row>
+    <row r="4" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="L4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="M4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="N4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="O4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="P4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="Q4" s="3" t="s">
+      <c r="Q4" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8"/>
-      <c r="N5" s="8"/>
-      <c r="O5" s="8"/>
-      <c r="P5" s="8"/>
-      <c r="Q5" s="8"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+    </row>
+    <row r="6" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="8">
         <v>2</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="9" t="s">
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="N6" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="M6" s="9" t="s">
+      <c r="O6" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="P6" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q6" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" s="8">
+        <v>2</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="M7" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="N6" s="10" t="s">
+      <c r="N7" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="O7" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="P7" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="O6" s="9" t="s">
+      <c r="Q7" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="E8" s="8">
+        <v>2</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="N8" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="O8" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="P6" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q6" s="9" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="D7" s="9" t="s">
+      <c r="P8" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q8" s="8" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
+    </row>
+    <row r="10" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="E10" s="8">
+        <v>2</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="M10" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="N10" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="O10" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="P10" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q10" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="E11" s="8">
+        <v>2</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="M11" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="N11" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="O11" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="P11" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q11" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="E12" s="8">
+        <v>2</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="N12" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="O12" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="P12" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q12" s="8" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="E13" s="8">
+        <v>2</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="M13" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="O13" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="P13" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q13" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="E14" s="8">
+        <v>2</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="M14" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="N14" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="O14" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="P14" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q14" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="E15" s="8">
+        <v>2</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="M15" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="N15" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="O15" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="P15" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q15" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="E16" s="8">
+        <v>2</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="M16" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="N16" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="O16" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="P16" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q16" s="8" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="7"/>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
+    </row>
+    <row r="18" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="E18" s="8">
+        <v>2</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="M18" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="N18" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="O18" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="P18" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q18" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="E19" s="8">
+        <v>2</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="M19" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="N19" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="O19" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="P19" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q19" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A20" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="E20" s="8">
+        <v>2</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="M20" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="N20" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="O20" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="P20" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q20" s="8" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="E21" s="8">
+        <v>2</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="M21" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="N21" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="O21" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="P21" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q21" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A22" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="E22" s="8">
+        <v>2</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="M22" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="N22" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="O22" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="P22" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q22" s="8" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="E23" s="8">
+        <v>2</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="M23" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="N23" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="O23" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="P23" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q23" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="E24" s="8">
+        <v>2</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="M24" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="N24" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="O24" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="P24" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q24" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A25" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="E25" s="8">
+        <v>2</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="M25" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="N25" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="O25" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="P25" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q25" s="8" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A26" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="E26" s="8">
+        <v>2</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="M26" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="N26" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="O26" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="P26" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q26" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A27" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="E27" s="8">
+        <v>2</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="M27" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="N27" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="O27" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="P27" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q27" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A29" s="10" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A30" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="D30" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E30" s="11">
         <v>2</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F30" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G30" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H30" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="M7" s="9" t="s">
+      <c r="I30" s="11">
+        <v>40</v>
+      </c>
+      <c r="J30" s="11">
+        <v>0</v>
+      </c>
+      <c r="K30" s="11">
+        <v>200</v>
+      </c>
+      <c r="L30" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="M30" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="N7" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="O7" s="9" t="s">
+      <c r="N30" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="O30" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="P7" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q7" s="9" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="E8" s="9">
-        <v>2</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="M8" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="N8" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="O8" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="P8" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q8" s="9" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="8"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="E10" s="9">
-        <v>2</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="M10" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="N10" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="O10" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="P10" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="Q10" s="9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="E11" s="9">
-        <v>2</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="M11" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="N11" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="O11" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="P11" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="Q11" s="9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="E12" s="9">
-        <v>2</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="M12" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="N12" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="O12" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="P12" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="Q12" s="9" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="E13" s="9">
-        <v>2</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="M13" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="N13" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="O13" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="P13" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="Q13" s="9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="E14" s="9">
-        <v>2</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="M14" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="N14" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="O14" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="P14" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="Q14" s="9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="E15" s="9">
-        <v>2</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="M15" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="N15" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="O15" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="P15" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="Q15" s="9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="E16" s="9">
-        <v>2</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="M16" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="N16" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="O16" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="P16" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="Q16" s="9" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
-      <c r="N17" s="8"/>
-      <c r="O17" s="8"/>
-      <c r="P17" s="8"/>
-      <c r="Q17" s="8"/>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="E18" s="9">
-        <v>2</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="M18" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="N18" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="O18" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="P18" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q18" s="9" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="E19" s="9">
-        <v>2</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="M19" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="N19" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="O19" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="P19" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q19" s="9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="E20" s="9">
-        <v>2</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="M20" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="N20" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="O20" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="P20" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q20" s="9" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="E21" s="9">
-        <v>2</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="M21" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="N21" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="O21" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="P21" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q21" s="9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="E22" s="9">
-        <v>2</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="M22" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="N22" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="O22" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="P22" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q22" s="9" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="E23" s="9">
-        <v>2</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
-      <c r="K23" s="10"/>
-      <c r="L23" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="M23" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="N23" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="O23" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="P23" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q23" s="9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="E24" s="9">
-        <v>2</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="G24" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="10"/>
-      <c r="L24" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="M24" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="N24" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="O24" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="P24" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q24" s="9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="E25" s="9">
-        <v>2</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="10"/>
-      <c r="L25" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="M25" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="N25" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="O25" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="P25" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q25" s="9" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A26" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="E26" s="9">
-        <v>2</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="G26" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H26" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
-      <c r="K26" s="10"/>
-      <c r="L26" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="M26" s="9" t="s">
-        <v>225</v>
-      </c>
-      <c r="N26" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="O26" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="P26" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q26" s="9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>228</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="E27" s="9">
-        <v>2</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="G27" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
-      <c r="K27" s="10"/>
-      <c r="L27" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="M27" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="N27" s="10" t="s">
-        <v>231</v>
-      </c>
-      <c r="O27" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="P27" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q27" s="9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="11" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A30" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="B30" s="12" t="s">
+      <c r="P30" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q30" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="C30" s="12" t="s">
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="D30" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="E30" s="12">
-        <v>2</v>
-      </c>
-      <c r="F30" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="G30" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="H30" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="I30" s="12">
-        <v>40</v>
-      </c>
-      <c r="J30" s="12">
-        <v>0</v>
-      </c>
-      <c r="K30" s="12">
-        <v>200</v>
-      </c>
-      <c r="L30" s="12" t="s">
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="M30" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="N30" s="12" t="s">
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="O30" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="P30" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q30" s="12" t="s">
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="13" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="13" t="s">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="13" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="14" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="13" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="14" t="s">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="13" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="14" t="s">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="13" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="14" t="s">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="12" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="14" t="s">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="14" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="14" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="14" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="13" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="15" t="s">
-        <v>248</v>
-      </c>
-      <c r="B44" s="15">
+      <c r="B44" s="14">
         <f>COUNTIF(D5:D27,"P1")</f>
         <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="15" t="s">
-        <v>249</v>
-      </c>
-      <c r="B45" s="15">
+      <c r="A45" s="14" t="s">
+        <v>245</v>
+      </c>
+      <c r="B45" s="14">
         <f>COUNTIF(D5:D27,"P2")</f>
         <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="15" t="s">
-        <v>250</v>
-      </c>
-      <c r="B46" s="15">
+      <c r="A46" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="B46" s="14">
         <f>COUNTIF(D5:D27,"P3")</f>
         <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="16" t="s">
-        <v>251</v>
-      </c>
-      <c r="B47" s="16">
+      <c r="A47" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="B47" s="15">
         <f>COUNTA(D5:D27)</f>
         <v>20</v>
       </c>
@@ -3119,6 +3136,6 @@
     <mergeCell ref="A2:H2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>